--- a/Practical3/Excel Sheets/STM32F0_Task2_Data.xlsx
+++ b/Practical3/Excel Sheets/STM32F0_Task2_Data.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://uctcloud-my.sharepoint.com/personal/ngrmar007_myuct_ac_za/Documents/Third Year/EEE3096s-repository/EEE3096S-Group-39/Practical3/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://uctcloud-my.sharepoint.com/personal/ngrmar007_myuct_ac_za/Documents/Third Year/EEE3096s-repository/EEE3096S-Group-39/Practical3/Excel Sheets/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="166" documentId="8_{B006F4A2-8E07-479D-A790-D971CA4F138D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FAEB412E-AFEC-4332-9053-261AA784B582}"/>
+  <xr:revisionPtr revIDLastSave="189" documentId="8_{B006F4A2-8E07-479D-A790-D971CA4F138D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{55892127-DFC8-4753-A37C-B6A586587A2A}"/>
   <bookViews>
-    <workbookView xWindow="-96" yWindow="0" windowWidth="11712" windowHeight="12336" xr2:uid="{C79BCD39-4858-4225-88C9-54642E139A6A}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{C79BCD39-4858-4225-88C9-54642E139A6A}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="7">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
   <si>
     <t>Iteration Value</t>
   </si>
@@ -57,6 +57,15 @@
   </si>
   <si>
     <t>Floating Point Arithmetic</t>
+  </si>
+  <si>
+    <t>Typical Voltage(V)</t>
+  </si>
+  <si>
+    <t>Current Consumed(A)</t>
+  </si>
+  <si>
+    <t>Power Consumed (Wh)</t>
   </si>
 </sst>
 </file>
@@ -98,10 +107,10 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -441,24 +450,27 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{877F171D-5667-4752-BDCE-0D09A4C5BA63}">
-  <dimension ref="A1:E51"/>
+  <dimension ref="A1:O51"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="21.77734375" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="18.6640625" style="1" customWidth="1"/>
-    <col min="3" max="3" width="20.33203125" style="3" customWidth="1"/>
+    <col min="3" max="3" width="20.33203125" style="2" customWidth="1"/>
     <col min="4" max="4" width="21.21875" style="1" customWidth="1"/>
     <col min="5" max="5" width="21.44140625" style="1" customWidth="1"/>
+    <col min="6" max="6" width="15.6640625" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="21.109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="13.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>4</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="C1" s="2" t="s">
         <v>1</v>
       </c>
       <c r="D1" s="1" t="s">
@@ -467,12 +479,21 @@
       <c r="E1" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2" s="2" t="s">
+      <c r="F1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="O1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A2" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="B2" s="2">
+      <c r="B2" s="3">
         <v>100</v>
       </c>
       <c r="C2" s="1">
@@ -484,10 +505,20 @@
       <c r="E2" s="1">
         <v>429284</v>
       </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A3" s="2"/>
-      <c r="B3" s="2"/>
+      <c r="F2">
+        <f>($N$2*$O$2*(D2/36000000))</f>
+        <v>7.7056833333333331E-6</v>
+      </c>
+      <c r="N2" s="1">
+        <v>2.1999999999999999E-2</v>
+      </c>
+      <c r="O2">
+        <v>3.3</v>
+      </c>
+    </row>
+    <row r="3" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A3" s="3"/>
+      <c r="B3" s="3"/>
       <c r="C3" s="1">
         <v>160</v>
       </c>
@@ -497,10 +528,14 @@
       <c r="E3" s="1">
         <v>670125</v>
       </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A4" s="2"/>
-      <c r="B4" s="2"/>
+      <c r="F3">
+        <f t="shared" ref="F3:F51" si="0">$N$2*$O$2*(D3/36000000)</f>
+        <v>1.2027399999999999E-5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A4" s="3"/>
+      <c r="B4" s="3"/>
       <c r="C4" s="1">
         <v>192</v>
       </c>
@@ -510,10 +545,14 @@
       <c r="E4" s="1">
         <v>966199</v>
       </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A5" s="2"/>
-      <c r="B5" s="2"/>
+      <c r="F4">
+        <f t="shared" si="0"/>
+        <v>1.7327199999999999E-5</v>
+      </c>
+    </row>
+    <row r="5" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A5" s="3"/>
+      <c r="B5" s="3"/>
       <c r="C5" s="1">
         <v>224</v>
       </c>
@@ -523,10 +562,14 @@
       <c r="E5" s="1">
         <v>1315228</v>
       </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A6" s="2"/>
-      <c r="B6" s="2"/>
+      <c r="F5">
+        <f t="shared" si="0"/>
+        <v>2.3572816666666666E-5</v>
+      </c>
+    </row>
+    <row r="6" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A6" s="3"/>
+      <c r="B6" s="3"/>
       <c r="C6" s="1">
         <v>256</v>
       </c>
@@ -536,10 +579,14 @@
       <c r="E6" s="1">
         <v>1716594</v>
       </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A7" s="2"/>
-      <c r="B7" s="2">
+      <c r="F6">
+        <f t="shared" si="0"/>
+        <v>3.0828783333333335E-5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A7" s="3"/>
+      <c r="B7" s="3">
         <v>250</v>
       </c>
       <c r="C7" s="1">
@@ -551,10 +598,14 @@
       <c r="E7" s="1">
         <v>967946</v>
       </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A8" s="2"/>
-      <c r="B8" s="2"/>
+      <c r="F7">
+        <f t="shared" si="0"/>
+        <v>1.5738066666666668E-5</v>
+      </c>
+    </row>
+    <row r="8" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A8" s="3"/>
+      <c r="B8" s="3"/>
       <c r="C8" s="1">
         <v>160</v>
       </c>
@@ -564,10 +615,14 @@
       <c r="E8" s="1">
         <v>1511166</v>
       </c>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A9" s="2"/>
-      <c r="B9" s="2"/>
+      <c r="F8">
+        <f t="shared" si="0"/>
+        <v>2.4571066666666666E-5</v>
+      </c>
+    </row>
+    <row r="9" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A9" s="3"/>
+      <c r="B9" s="3"/>
       <c r="C9" s="1">
         <v>192</v>
       </c>
@@ -577,10 +632,14 @@
       <c r="E9" s="1">
         <v>2181757</v>
       </c>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A10" s="2"/>
-      <c r="B10" s="2"/>
+      <c r="F9">
+        <f t="shared" si="0"/>
+        <v>3.5457033333333336E-5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A10" s="3"/>
+      <c r="B10" s="3"/>
       <c r="C10" s="1">
         <v>224</v>
       </c>
@@ -590,10 +649,14 @@
       <c r="E10" s="1">
         <v>2965729</v>
       </c>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A11" s="2"/>
-      <c r="B11" s="2"/>
+      <c r="F10">
+        <f t="shared" si="0"/>
+        <v>4.8190266666666665E-5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A11" s="3"/>
+      <c r="B11" s="3"/>
       <c r="C11" s="1">
         <v>256</v>
       </c>
@@ -603,10 +666,14 @@
       <c r="E11" s="1">
         <v>3873352</v>
       </c>
-    </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A12" s="2"/>
-      <c r="B12" s="2">
+      <c r="F11">
+        <f t="shared" si="0"/>
+        <v>6.299865E-5</v>
+      </c>
+    </row>
+    <row r="12" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A12" s="3"/>
+      <c r="B12" s="3">
         <v>500</v>
       </c>
       <c r="C12" s="1">
@@ -618,10 +685,14 @@
       <c r="E12" s="1">
         <v>1857678</v>
       </c>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A13" s="2"/>
-      <c r="B13" s="2"/>
+      <c r="F12">
+        <f t="shared" si="0"/>
+        <v>2.9007733333333334E-5</v>
+      </c>
+    </row>
+    <row r="13" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A13" s="3"/>
+      <c r="B13" s="3"/>
       <c r="C13" s="1">
         <v>160</v>
       </c>
@@ -631,10 +702,14 @@
       <c r="E13" s="1">
         <v>2900031</v>
       </c>
-    </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A14" s="2"/>
-      <c r="B14" s="2"/>
+      <c r="F13">
+        <f t="shared" si="0"/>
+        <v>4.5286266666666667E-5</v>
+      </c>
+    </row>
+    <row r="14" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A14" s="3"/>
+      <c r="B14" s="3"/>
       <c r="C14" s="1">
         <v>192</v>
       </c>
@@ -644,10 +719,14 @@
       <c r="E14" s="1">
         <v>4188264</v>
       </c>
-    </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A15" s="2"/>
-      <c r="B15" s="2"/>
+      <c r="F14">
+        <f t="shared" si="0"/>
+        <v>6.5382350000000003E-5</v>
+      </c>
+    </row>
+    <row r="15" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A15" s="3"/>
+      <c r="B15" s="3"/>
       <c r="C15" s="1">
         <v>224</v>
       </c>
@@ -657,10 +736,14 @@
       <c r="E15" s="1">
         <v>5690272</v>
       </c>
-    </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A16" s="2"/>
-      <c r="B16" s="2"/>
+      <c r="F15">
+        <f t="shared" si="0"/>
+        <v>8.88261E-5</v>
+      </c>
+    </row>
+    <row r="16" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A16" s="3"/>
+      <c r="B16" s="3"/>
       <c r="C16" s="1">
         <v>256</v>
       </c>
@@ -670,10 +753,14 @@
       <c r="E16" s="1">
         <v>7436300</v>
       </c>
-    </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A17" s="2"/>
-      <c r="B17" s="2">
+      <c r="F16">
+        <f t="shared" si="0"/>
+        <v>1.1613781666666665E-4</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A17" s="3"/>
+      <c r="B17" s="3">
         <v>750</v>
       </c>
       <c r="C17" s="1">
@@ -685,10 +772,14 @@
       <c r="E17" s="1">
         <v>2745748</v>
       </c>
-    </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A18" s="2"/>
-      <c r="B18" s="2"/>
+      <c r="F17">
+        <f t="shared" si="0"/>
+        <v>4.2253200000000004E-5</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A18" s="3"/>
+      <c r="B18" s="3"/>
       <c r="C18" s="1">
         <v>160</v>
       </c>
@@ -698,10 +789,14 @@
       <c r="E18" s="1">
         <v>4284306</v>
       </c>
-    </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A19" s="2"/>
-      <c r="B19" s="2"/>
+      <c r="F18">
+        <f t="shared" si="0"/>
+        <v>6.5930883333333333E-5</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A19" s="3"/>
+      <c r="B19" s="3"/>
       <c r="C19" s="1">
         <v>192</v>
       </c>
@@ -711,10 +806,14 @@
       <c r="E19" s="1">
         <v>6190623</v>
       </c>
-    </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A20" s="2"/>
-      <c r="B20" s="2"/>
+      <c r="F19">
+        <f t="shared" si="0"/>
+        <v>9.5247166666666651E-5</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A20" s="3"/>
+      <c r="B20" s="3"/>
       <c r="C20" s="1">
         <v>224</v>
       </c>
@@ -724,10 +823,14 @@
       <c r="E20" s="1">
         <v>8408947</v>
       </c>
-    </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A21" s="2"/>
-      <c r="B21" s="2"/>
+      <c r="F20">
+        <f t="shared" si="0"/>
+        <v>1.293732E-4</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A21" s="3"/>
+      <c r="B21" s="3"/>
       <c r="C21" s="1">
         <v>256</v>
       </c>
@@ -737,10 +840,14 @@
       <c r="E21" s="1">
         <v>10990550</v>
       </c>
-    </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A22" s="2"/>
-      <c r="B22" s="2">
+      <c r="F21">
+        <f t="shared" si="0"/>
+        <v>1.6914791666666667E-4</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A22" s="3"/>
+      <c r="B22" s="3">
         <v>1000</v>
       </c>
       <c r="C22" s="1">
@@ -752,10 +859,14 @@
       <c r="E22" s="1">
         <v>3632998</v>
       </c>
-    </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A23" s="2"/>
-      <c r="B23" s="2"/>
+      <c r="F22">
+        <f t="shared" si="0"/>
+        <v>5.5486566666666665E-5</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A23" s="3"/>
+      <c r="B23" s="3"/>
       <c r="C23" s="1">
         <v>160</v>
       </c>
@@ -765,10 +876,14 @@
       <c r="E23" s="1">
         <v>5667029</v>
       </c>
-    </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A24" s="2"/>
-      <c r="B24" s="2"/>
+      <c r="F23">
+        <f t="shared" si="0"/>
+        <v>8.6553316666666667E-5</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A24" s="3"/>
+      <c r="B24" s="3"/>
       <c r="C24" s="1">
         <v>192</v>
       </c>
@@ -778,10 +893,14 @@
       <c r="E24" s="1">
         <v>8190158</v>
       </c>
-    </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A25" s="2"/>
-      <c r="B25" s="2"/>
+      <c r="F24">
+        <f t="shared" si="0"/>
+        <v>1.2506963333333335E-4</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A25" s="3"/>
+      <c r="B25" s="3"/>
       <c r="C25" s="1">
         <v>224</v>
       </c>
@@ -791,10 +910,14 @@
       <c r="E25" s="1">
         <v>11124625</v>
       </c>
-    </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A26" s="2"/>
-      <c r="B26" s="2"/>
+      <c r="F25">
+        <f t="shared" si="0"/>
+        <v>1.6987795E-4</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A26" s="3"/>
+      <c r="B26" s="3"/>
       <c r="C26" s="1">
         <v>256</v>
       </c>
@@ -804,12 +927,16 @@
       <c r="E26" s="1">
         <v>14538990</v>
       </c>
-    </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A27" s="2" t="s">
+      <c r="F26">
+        <f t="shared" si="0"/>
+        <v>2.220713E-4</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A27" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="B27" s="2">
+      <c r="B27" s="3">
         <v>100</v>
       </c>
       <c r="C27" s="1">
@@ -821,10 +948,14 @@
       <c r="E27" s="1">
         <v>429384</v>
       </c>
-    </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A28" s="2"/>
-      <c r="B28" s="2"/>
+      <c r="F27">
+        <f t="shared" si="0"/>
+        <v>4.4298099999999995E-5</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A28" s="3"/>
+      <c r="B28" s="3"/>
       <c r="C28" s="1">
         <v>160</v>
       </c>
@@ -834,10 +965,14 @@
       <c r="E28" s="1">
         <v>669829</v>
       </c>
-    </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A29" s="2"/>
-      <c r="B29" s="2"/>
+      <c r="F28">
+        <f t="shared" si="0"/>
+        <v>6.9869433333333332E-5</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A29" s="3"/>
+      <c r="B29" s="3"/>
       <c r="C29" s="1">
         <v>192</v>
       </c>
@@ -847,10 +982,14 @@
       <c r="E29" s="1">
         <v>966024</v>
       </c>
-    </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A30" s="2"/>
-      <c r="B30" s="2"/>
+      <c r="F29">
+        <f t="shared" si="0"/>
+        <v>1.00672E-4</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A30" s="3"/>
+      <c r="B30" s="3"/>
       <c r="C30" s="1">
         <v>224</v>
       </c>
@@ -860,10 +999,14 @@
       <c r="E30" s="1">
         <v>1314999</v>
       </c>
-    </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A31" s="2"/>
-      <c r="B31" s="2"/>
+      <c r="F30">
+        <f t="shared" si="0"/>
+        <v>1.3731281666666667E-4</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A31" s="3"/>
+      <c r="B31" s="3"/>
       <c r="C31" s="1">
         <v>256</v>
       </c>
@@ -873,10 +1016,14 @@
       <c r="E31" s="1">
         <v>1715812</v>
       </c>
-    </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A32" s="2"/>
-      <c r="B32" s="2">
+      <c r="F31">
+        <f t="shared" si="0"/>
+        <v>1.7748683333333333E-4</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A32" s="3"/>
+      <c r="B32" s="3">
         <v>250</v>
       </c>
       <c r="C32" s="1">
@@ -888,10 +1035,14 @@
       <c r="E32" s="1">
         <v>968444</v>
       </c>
-    </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A33" s="2"/>
-      <c r="B33" s="2"/>
+      <c r="F32">
+        <f t="shared" si="0"/>
+        <v>9.8001933333333334E-5</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A33" s="3"/>
+      <c r="B33" s="3"/>
       <c r="C33" s="1">
         <v>160</v>
       </c>
@@ -901,10 +1052,14 @@
       <c r="E33" s="1">
         <v>1509977</v>
       </c>
-    </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A34" s="2"/>
-      <c r="B34" s="2"/>
+      <c r="F33">
+        <f t="shared" si="0"/>
+        <v>1.5365789999999998E-4</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A34" s="3"/>
+      <c r="B34" s="3"/>
       <c r="C34" s="1">
         <v>192</v>
       </c>
@@ -914,10 +1069,14 @@
       <c r="E34" s="1">
         <v>2179882</v>
       </c>
-    </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A35" s="2"/>
-      <c r="B35" s="2"/>
+      <c r="F34">
+        <f t="shared" si="0"/>
+        <v>2.2182526666666665E-4</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A35" s="3"/>
+      <c r="B35" s="3"/>
       <c r="C35" s="1">
         <v>224</v>
       </c>
@@ -927,10 +1086,14 @@
       <c r="E35" s="1">
         <v>2963391</v>
       </c>
-    </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A36" s="2"/>
-      <c r="B36" s="2"/>
+      <c r="F35">
+        <f t="shared" si="0"/>
+        <v>3.0192323333333334E-4</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A36" s="3"/>
+      <c r="B36" s="3"/>
       <c r="C36" s="1">
         <v>256</v>
       </c>
@@ -940,10 +1103,14 @@
       <c r="E36" s="1">
         <v>3873086</v>
       </c>
-    </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A37" s="2"/>
-      <c r="B37" s="2">
+      <c r="F36">
+        <f t="shared" si="0"/>
+        <v>3.9307454999999995E-4</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A37" s="3"/>
+      <c r="B37" s="3">
         <v>500</v>
       </c>
       <c r="C37" s="1">
@@ -955,10 +1122,14 @@
       <c r="E37" s="1">
         <v>1857698</v>
       </c>
-    </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A38" s="2"/>
-      <c r="B38" s="2"/>
+      <c r="F37">
+        <f t="shared" si="0"/>
+        <v>1.8659611666666667E-4</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A38" s="3"/>
+      <c r="B38" s="3"/>
       <c r="C38" s="1">
         <v>160</v>
       </c>
@@ -968,10 +1139,14 @@
       <c r="E38" s="1">
         <v>2898149</v>
       </c>
-    </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A39" s="2"/>
-      <c r="B39" s="2"/>
+      <c r="F38">
+        <f t="shared" si="0"/>
+        <v>2.9211819999999997E-4</v>
+      </c>
+    </row>
+    <row r="39" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A39" s="3"/>
+      <c r="B39" s="3"/>
       <c r="C39" s="1">
         <v>192</v>
       </c>
@@ -981,10 +1156,14 @@
       <c r="E39" s="1">
         <v>4182966</v>
       </c>
-    </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A40" s="2"/>
-      <c r="B40" s="2"/>
+      <c r="F39">
+        <f t="shared" si="0"/>
+        <v>4.2175961666666669E-4</v>
+      </c>
+    </row>
+    <row r="40" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A40" s="3"/>
+      <c r="B40" s="3"/>
       <c r="C40" s="1">
         <v>224</v>
       </c>
@@ -994,10 +1173,14 @@
       <c r="E40" s="1">
         <v>5683767</v>
       </c>
-    </row>
-    <row r="41" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A41" s="2"/>
-      <c r="B41" s="2"/>
+      <c r="F40">
+        <f t="shared" si="0"/>
+        <v>5.7360856666666669E-4</v>
+      </c>
+    </row>
+    <row r="41" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A41" s="3"/>
+      <c r="B41" s="3"/>
       <c r="C41" s="1">
         <v>256</v>
       </c>
@@ -1007,10 +1190,14 @@
       <c r="E41" s="1">
         <v>7437312</v>
       </c>
-    </row>
-    <row r="42" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A42" s="2"/>
-      <c r="B42" s="2">
+      <c r="F41">
+        <f t="shared" si="0"/>
+        <v>7.4930863333333333E-4</v>
+      </c>
+    </row>
+    <row r="42" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A42" s="3"/>
+      <c r="B42" s="3">
         <v>750</v>
       </c>
       <c r="C42" s="1">
@@ -1022,10 +1209,14 @@
       <c r="E42" s="1">
         <v>2744850</v>
       </c>
-    </row>
-    <row r="43" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A43" s="2"/>
-      <c r="B43" s="2"/>
+      <c r="F42">
+        <f t="shared" si="0"/>
+        <v>2.7497653333333335E-4</v>
+      </c>
+    </row>
+    <row r="43" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A43" s="3"/>
+      <c r="B43" s="3"/>
       <c r="C43" s="1">
         <v>160</v>
       </c>
@@ -1035,10 +1226,14 @@
       <c r="E43" s="1">
         <v>4280860</v>
       </c>
-    </row>
-    <row r="44" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A44" s="2"/>
-      <c r="B44" s="2"/>
+      <c r="F43">
+        <f t="shared" si="0"/>
+        <v>4.3003601666666665E-4</v>
+      </c>
+    </row>
+    <row r="44" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A44" s="3"/>
+      <c r="B44" s="3"/>
       <c r="C44" s="1">
         <v>192</v>
       </c>
@@ -1048,10 +1243,14 @@
       <c r="E44" s="1">
         <v>6180580</v>
       </c>
-    </row>
-    <row r="45" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A45" s="2"/>
-      <c r="B45" s="2"/>
+      <c r="F44">
+        <f t="shared" si="0"/>
+        <v>6.2115148333333333E-4</v>
+      </c>
+    </row>
+    <row r="45" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A45" s="3"/>
+      <c r="B45" s="3"/>
       <c r="C45" s="1">
         <v>224</v>
       </c>
@@ -1061,10 +1260,14 @@
       <c r="E45" s="1">
         <v>8399191</v>
       </c>
-    </row>
-    <row r="46" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A46" s="2"/>
-      <c r="B46" s="2"/>
+      <c r="F45">
+        <f t="shared" si="0"/>
+        <v>8.4480788333333328E-4</v>
+      </c>
+    </row>
+    <row r="46" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A46" s="3"/>
+      <c r="B46" s="3"/>
       <c r="C46" s="1">
         <v>256</v>
       </c>
@@ -1074,10 +1277,14 @@
       <c r="E46" s="1">
         <v>10988990</v>
       </c>
-    </row>
-    <row r="47" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A47" s="2"/>
-      <c r="B47" s="2">
+      <c r="F46">
+        <f t="shared" si="0"/>
+        <v>1.1043105333333333E-3</v>
+      </c>
+    </row>
+    <row r="47" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A47" s="3"/>
+      <c r="B47" s="3">
         <v>1000</v>
       </c>
       <c r="C47" s="1">
@@ -1089,10 +1296,14 @@
       <c r="E47" s="1">
         <v>3631126</v>
       </c>
-    </row>
-    <row r="48" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A48" s="2"/>
-      <c r="B48" s="2"/>
+      <c r="F47">
+        <f t="shared" si="0"/>
+        <v>3.6327426666666669E-4</v>
+      </c>
+    </row>
+    <row r="48" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A48" s="3"/>
+      <c r="B48" s="3"/>
       <c r="C48" s="1">
         <v>160</v>
       </c>
@@ -1102,10 +1313,14 @@
       <c r="E48" s="1">
         <v>5661614</v>
       </c>
-    </row>
-    <row r="49" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A49" s="2"/>
-      <c r="B49" s="2"/>
+      <c r="F48">
+        <f t="shared" si="0"/>
+        <v>5.6776224999999995E-4</v>
+      </c>
+    </row>
+    <row r="49" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A49" s="3"/>
+      <c r="B49" s="3"/>
       <c r="C49" s="1">
         <v>192</v>
       </c>
@@ -1115,10 +1330,14 @@
       <c r="E49" s="1">
         <v>8176148</v>
       </c>
-    </row>
-    <row r="50" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A50" s="2"/>
-      <c r="B50" s="2"/>
+      <c r="F49">
+        <f t="shared" si="0"/>
+        <v>8.2033966666666676E-4</v>
+      </c>
+    </row>
+    <row r="50" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A50" s="3"/>
+      <c r="B50" s="3"/>
       <c r="C50" s="1">
         <v>224</v>
       </c>
@@ -1128,10 +1347,14 @@
       <c r="E50" s="1">
         <v>11112491</v>
       </c>
-    </row>
-    <row r="51" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A51" s="2"/>
-      <c r="B51" s="2"/>
+      <c r="F50">
+        <f t="shared" si="0"/>
+        <v>1.1157974666666667E-3</v>
+      </c>
+    </row>
+    <row r="51" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A51" s="3"/>
+      <c r="B51" s="3"/>
       <c r="C51" s="1">
         <v>256</v>
       </c>
@@ -1141,21 +1364,25 @@
       <c r="E51" s="1">
         <v>14534966</v>
       </c>
+      <c r="F51">
+        <f t="shared" si="0"/>
+        <v>1.4587538166666667E-3</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="12">
+    <mergeCell ref="A27:A51"/>
+    <mergeCell ref="B27:B31"/>
+    <mergeCell ref="B32:B36"/>
+    <mergeCell ref="B37:B41"/>
+    <mergeCell ref="B42:B46"/>
+    <mergeCell ref="B47:B51"/>
     <mergeCell ref="A2:A26"/>
     <mergeCell ref="B2:B6"/>
     <mergeCell ref="B7:B11"/>
     <mergeCell ref="B12:B16"/>
     <mergeCell ref="B17:B21"/>
     <mergeCell ref="B22:B26"/>
-    <mergeCell ref="A27:A51"/>
-    <mergeCell ref="B27:B31"/>
-    <mergeCell ref="B32:B36"/>
-    <mergeCell ref="B37:B41"/>
-    <mergeCell ref="B42:B46"/>
-    <mergeCell ref="B47:B51"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
